--- a/public/compliance/papyrus/papyrus-controls-matrix.xlsx
+++ b/public/compliance/papyrus/papyrus-controls-matrix.xlsx
@@ -5,7 +5,7 @@
     <sheet name="Controls" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Controls'!$A$1:$J$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Controls'!$A$1:$J$51</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -144,38 +144,38 @@
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">implemented</t>
+          <t xml:space="preserve">partial</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Papyrus creates no local user accounts or passwords; every person is a Microsoft Entra identity (tenant ID and object ID) and authority comes only from the eleven declared Papyrus roles. On deployments that sign in through Beag Labs, roles live in a Papyrus role-assignment table: the consenting admin is seeded as the first System Owner, only a System Owner (never an API key) can grant or revoke roles, the last System Owner cannot be revoked, and every grant and revocation is written to an append-only event table protected by database triggers. Automation uses API keys, which are service identities with no roles that name the workflows they may run, expire after 1 to 365 days (default 90), and can be rotated or revoked with creation, rotation, revocation and last use recorded.</t>
+          <t xml:space="preserve">Papyrus creates no local user accounts or passwords; every person is an identity from the organization's OpenID Connect provider or Microsoft Entra ID, configured in papyrus.yaml, and authority comes only from the declared Papyrus roles, from token or directory-group claims mapped in papyrus.yaml, or from Papyrus role assignments. There is no first-run setup page: the first System Owners are named in papyrus.yaml (identity.owners) and receive the role when they first sign in. Only a System Owner (never an API key) can grant or revoke roles, the last System Owner cannot be revoked, and every grant and revocation is written to an append-only event table. With SCIM 2.0 provisioning on, a person the directory deprovisions or deactivates loses access on their next request. Automation uses API keys: service identities with no roles that name the workflows they may run and expire after 1 to 365 days (default 90).</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Own the account lifecycle in Entra ID: identity proofing, approval of app-role assignments, periodic access review, disabling departed users, and guest policy. Review Papyrus role assignments and API keys on the organization's review cadence.</t>
+          <t xml:space="preserve">Own the account lifecycle in the identity provider (proofing, approval, periodic review, removal), name the first System Owners in papyrus.yaml, and review Papyrus role assignments and API keys on the organization's cadence.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/src/agent/entra-auth.ts (principalFromClaims keeps only declared Papyrus app roles; withAssignedRoles reads Papyrus assignments on every request)
-apps/server/src/agent/role-assignments.ts (Role assignment table, append-only event log via UPDATE/DELETE triggers, last-System-Owner guard, first-owner seeding)
-apps/server/src/agent/http.ts (/api/access/assignments refuses API keys and requires Papyrus.System.Owner)
-apps/server/src/agent/api-keys.ts (API key service identities: expiry bounds, rotation, revocation, last-used tracking)
-packages/contracts/src/index.ts (ENTRA_APP_ROLES: the eleven declared Papyrus roles)</t>
+          <t xml:space="preserve">apps/server/src/agent/auth.ts (principalFromClaims and group mappings; grantConfiguredOwner grants identity.owners at sign-in; withDirectory checks SCIM status per request)
+apps/server/src/agent/role-assignments.ts (Append-only role events, last-System-Owner guard)
+apps/server/src/agent/config.ts (loadConfig refuses to start without an identity provider; no setup phase)
+apps/server/src/agent/api-keys.ts (Workflow-scoped API keys: expiry, rotation, revocation, last use)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-auth.test.ts (Maps only declared Entra app roles and never provisions local roles)
-apps/server/tests/agent-microsoft-broker.test.ts (Grants, lists and revokes assignments, never removes the last System Owner; a revoked role ends on the next request)
-apps/server/tests/api-keys.test.ts (Key expiry, revocation, rotation, last-use recording and roleless service identity)</t>
+apps/server/tests/api-keys.test.ts (Key expiry, revocation, rotation, last-use recording and roleless service identity)
+apps/server/tests/agent-role-assignments.test.ts (Grants, lists and revokes assignments, never removes the last System Owner)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A person who holds System Owner through a Papyrus role assignment keeps access while SCIM reports them deprovisioned (intended as break-glass), and there is no administrator action to end a person's active sessions.
+Remediation: Limit the SCIM bypass to accounts named in papyrus.yaml and audit each use; add a System Owner action to revoke a person's sessions.</t>
         </is>
       </c>
     </row>
@@ -207,20 +207,19 @@
       </c>
       <c r="F3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Every protected HTTP route authenticates the caller server-side and rejects principals that hold no Papyrus role; administrative, integration, approval, audit and owner-only operations check the specific role on the server before acting. MCP servers, imported APIs, Resource Classes and API keys are scoped to the caller's tenant, and an API key is admitted only to start runs of the workflows it names and read the runs it started. Sensitive Resource Class fields are masked except for administrators and the Class's sensitive-reader groups.</t>
+          <t xml:space="preserve">Every protected HTTP route authenticates the caller server-side and rejects principals that hold no Papyrus role; administrative, integration, approval, audit and owner-only operations check the specific role on the server before acting. Until a System Owner accepts the current Terms of Service and Privacy Policy in the app, only sign-in, the terms and health routes answer. MCP servers, imported APIs and API keys are scoped to the caller's tenant, and an API key is admitted only to start runs of the workflows it names and read the runs it started. Named agents run only from an active, signed revision; within a session an agent may use any tool the deployment offers, and whether a tool call needs a person's approval is decided by the tool's permission policy and, for MCP tools, the administrator's classification.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Assign Papyrus roles in Entra (or on the Access page for brokered deployments) according to organizational need-to-know.</t>
+          <t xml:space="preserve">Assign Papyrus roles in Entra according to organizational need-to-know.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/src/agent/http.ts (principal(), requireRole and requireAnyRole on each route; API key route restriction for /api/v1/workflows)
-apps/server/src/agent/service.ts (requirePortalAccess rejects principals with no role; approve/deny require Papyrus.Action.Approve)
-apps/server/src/agent/mcp/servers.ts (MCP server lookup enforces tenant match)
-apps/server/src/agent/mastra/runtime.ts (Sessions are owned by the tenant resource id (resourceId), not by individual users)</t>
+          <t xml:space="preserve">apps/server/src/agent/http.ts (requireRole/requireAnyRole on routes; TERMS_NOT_ACCEPTED gate (LEGAL_EXEMPT))
+apps/server/src/agent/roster/store.ts (assertSession requires an active signed revision; beforeTool enforces budgets)
+apps/server/src/agent/mastra/native-runtime.ts (Tool permission policies (allow/ask) per tool and MCP classification)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="2">
@@ -266,7 +265,7 @@
       </c>
       <c r="F4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Papyrus enforces several fixed flow rules in code: agent workspace commands run with network access denied (Factory sidecar commands do not; see sc-39); Hosted App frames carry connect-src 'none' and reach data only through brokered, operation-specific connector grants; credentials are resolved by trusted runtime code and never passed to models, App source or workspace processes; MCP tool results are labeled as external content and truncated at 64 KiB; and public intake can write only an endpoint's allow-listed fields and never person, group or reference fields. Outbound HTTP from workflows, MCP, imported APIs and Class endpoint sends must use HTTPS to a public address unless the host is explicitly listed as internal, may not embed credentials, and never follows redirects.</t>
+          <t xml:space="preserve">Papyrus enforces fixed flow rules in code: agent workspace commands run with network access denied; repository imports and package installs are downloaded by the server, never the sandbox, and nothing in them runs; credentials are resolved by trusted runtime code and never passed to models or workspace processes; MCP tool results are labeled as external content. Outbound requests made for workflow HTTP steps, link previews, MCP servers and repository imports pass an egress gate: with egress.allowedHosts set in papyrus.yaml only listed hosts (names or *.suffix) are reached, and on the disconnected profile nothing outside the boundary is reached until it is listed.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="2">
@@ -276,25 +275,23 @@
       </c>
       <c r="H4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/src/agent/mastra/workflow-runtime-tools.ts (assertWorkflowHttpTarget: HTTPS, no URL credentials, denylist, refusal of non-public resolved addresses)
-apps/server/src/agent/mcp/calls.ts (Results labeled external-mcp-server and truncated at 64 KiB)
-apps/server/src/agent/apps/http.ts (Hosted App frame CSP with connect-src 'none')
-apps/server/src/agent/mastra/workspace-nono-worker.ts (Sandbox policy sets allowNetwork false and refuses to run unless network is resolved as restricted)
-apps/server/src/agent/classes/endpoints.ts (Endpoint field allow-lists and per-endpoint limits for public intake)</t>
+          <t xml:space="preserve">apps/server/src/agent/egress.ts (assertEgressAllowed: allow-list, default deny on disconnected)
+apps/server/src/agent/mastra/workflow-runtime-tools.ts (Workflow HTTP targets checked against the gate)
+apps/server/src/agent/mastra/fetch-preview.ts (Link previews checked against the gate)
+apps/server/src/agent/mcp/connect.ts (MCP servers checked against the gate)
+apps/server/src/agent/repository-import.ts (Every redirect hop checked; links and paths outside the target skipped)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/tests/workflow-http-target.test.ts (Rejects plain HTTP, embedded credentials, denylisted hosts and non-public addresses)
-apps/server/tests/agent-app-runtime-boundary.test.ts (Rejects ambient secrets, direct browser networking and credential literals in App source)
-apps/server/tests/agent-workspace.test.ts (Papyrus credentials are not passed into workspace child processes)
-apps/server/tests/agent-class-endpoints-http.test.ts (Public forms take only their configured fields)</t>
+          <t xml:space="preserve">apps/server/tests/agent-egress.test.ts (Default deny on disconnected, listed hosts, wildcard matching)
+apps/server/tests/agent-repository-import.test.ts (Redirect hosts checked against the allow-list)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Outbound HTTP from workflow http-get/http-post steps and imported API tools is allowed to any public HTTPS host by default; the organization can block hosts with a denylist but there is no allow-list-only mode.
-Remediation: Add an allow-list mode (deny by default) for workflow and imported-API egress, selectable per deployment profile and on by default for the government and disconnected profiles.</t>
+          <t xml:space="preserve">Model gateway, identity provider discovery and Sentry connections do not pass the egress gate (they are configured endpoints), and the gate does not pin the resolved address, so a host that changes its DNS answer between check and connect could reach an internal address.
+Remediation: Route every outbound connection through the gate and connect to the address that was checked.</t>
         </is>
       </c>
     </row>
@@ -326,7 +323,7 @@
       </c>
       <c r="F5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The agent can propose but cannot approve: approveProposal, denyProposal and executeAction are rejected at the agent tool layer, and approval routes require a human Entra session holding Papyrus.Action.Approve. Workflow approval steps addressed to a person or group can be answered only by that person, a member of that group, or a System Owner, never by the person who started the run. Authority-weakening policy changes, non-additive Class changes and App publications wait for a Governance principal (System Owner, or Security.Manage plus Action.Approve).</t>
+          <t xml:space="preserve">The agent can propose but cannot approve: approveProposal, denyProposal and executeAction are rejected at the agent tool layer, and approval routes require a human Entra session holding Papyrus.Action.Approve. Workflow approval steps addressed to a person or group can be answered only by that person, a member of that group, or a System Owner, never by the person who started the run. Authority-weakening policy changes wait for a Governance principal (System Owner, or Security.Manage plus Action.Approve).</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="2">
@@ -383,7 +380,7 @@
       </c>
       <c r="F6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Papyrus splits authority into roles (integration view and manage, security manage, action approve, audit view and system owner) and checks the narrowest one per operation; Papyrus.System.Owner implies all of them. API keys hold no roles. Customer agents receive only read tools for their configured Classes and run as the requesting person. The container runs as a non-root user, and workspace commands run with the data directory unreadable and network denied.</t>
+          <t xml:space="preserve">Papyrus splits authority into roles (integration view and manage, security manage, action approve, audit view and system owner) and checks the narrowest one per operation; Papyrus.System.Owner implies all of them. API keys hold no roles. The container runs as a non-root user, and workspace commands run with the data directory unreadable and network denied.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="2">
@@ -394,16 +391,14 @@
       <c r="H6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">packages/contracts/src/index.ts (ENTRA_APP_ROLES and OBSERVABILITY_APP_ROLES)
-apps/server/src/agent/entra-auth.ts (hasAppRole: System Owner implies every role)
+apps/server/src/agent/auth.ts (hasAppRole: System Owner implies every role)
 apps/server/src/agent/entra-app-setup.ts (Role descriptions declared on the Entra app)
-Dockerfile (USER nonroot in the runtime stage)
-apps/server/src/agent/customer-agents/store.ts (Customer agents limited to configured Classes)</t>
+Dockerfile (USER nonroot in the runtime stage)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/tests/agent-auth.test.ts (System Owner role is treated as all portal permissions)
-apps/server/tests/agent-customer-agents.test.ts (Customer agent tool and class scoping)</t>
+          <t xml:space="preserve">apps/server/tests/agent-auth.test.ts (System Owner role is treated as all portal permissions)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr" s="2">
@@ -441,7 +436,7 @@
       </c>
       <c r="F7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Papyrus accepts no passwords, so interactive logon attempts and lockout are handled by Microsoft Entra ID. For the one Papyrus-managed secret a member of the public can guess, Resource Class request links with a confirmation question lock permanently after five wrong answers. Invalid, expired, revoked and rotated API keys all receive the same 401 response.</t>
+          <t xml:space="preserve">Papyrus accepts no passwords, so interactive logon attempts and lockout are handled by the identity provider. Every completed and failed sign-in callback is written to the audit trail with the client address. Workflow webhook secrets are 256 random bits made by the server, and invalid, expired, revoked and rotated API keys all receive the same 401.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr" s="2">
@@ -451,13 +446,13 @@
       </c>
       <c r="H7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/src/agent/classes/requests.ts (MAX_FAILED_CHECKS = 5; request link status set to locked)
-apps/server/src/agent/http.ts (Uniform 401 API_KEY_INVALID for any unusable key)</t>
+          <t xml:space="preserve">apps/server/src/agent/http.ts (auth.sign_in success and failure audit records on the OIDC/Entra callback)
+apps/server/src/agent/api-keys.ts (Uniform 401 for bad keys)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/tests/agent-class-requests-webhooks.test.ts (Request links lock after five wrong answers)
+          <t xml:space="preserve">apps/server/tests/agent-workflow-webhook-http.test.ts (Bad and missing signatures get 401; a rotated-away secret stops working)
 apps/server/tests/agent-api-keys-http.test.ts (Missing, malformed, revoked or rotated-away keys get the same answer)</t>
         </is>
       </c>
@@ -470,12 +465,12 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AC-12</t>
+          <t xml:space="preserve">AC-8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Session Termination</t>
+          <t xml:space="preserve">System Use Notification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
@@ -490,622 +485,884 @@
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">partial</t>
+          <t xml:space="preserve">implemented</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The portal session is an HMAC-signed cookie with a one-hour lifetime whose expiry is checked server-side; after it expires the person must sign in through Entra again. Sign-out clears the cookie. On brokered deployments roles are re-read from the assignment table on every request, so revoking a person's roles ends their access on the next request.</t>
+          <t xml:space="preserve">With security.notice set in papyrus.yaml, Papyrus shows the system use notice before sign-in (dow for the standard DoD notice and consent banner, or the organization's own text from a file) and starts sign-in only after the person consents. Each acknowledgement is recorded in the audit trail with the notice's digest and the client address.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Set Entra token lifetimes and Conditional Access sign-in frequency; use boundary controls if faster revocation is required.</t>
+          <t xml:space="preserve">Choose the notice text approved for the system and set security.notice.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/src/agent/entra-auth.ts (portalCookie Max-Age=3600 with signed exp; verifyPortalCookie rejects expired cookies; clearCookie)
-apps/server/src/agent/http.ts (/api/auth/logout clears the cookie)</t>
+          <t xml:space="preserve">apps/server/src/agent/http.ts (DOW_NOTICE, systemNotice; login refused without the acknowledged digest; auth.notice_acknowledged record)
+apps/web/src/App.tsx (Notice screen before the sign-in button)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">apps/server/tests/agent-microsoft-broker.test.ts (A revoked role ends at once on brokered deployments)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sessions are stateless: there is no server-side session store, idle timeout, or revocation list. A copied cookie remains valid until its one-hour expiry after sign-out, and on deployments using their own app registration the roles carried in the cookie persist until expiry after an Entra role is removed.
-Remediation: Add a server-side session table with idle timeout, explicit revocation on sign-out, and an administrator action to end a person's sessions.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">AC-10</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Concurrent Session Control</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Access Control</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">provider</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">implemented</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Each person may hold at most three portal sessions at once by default (security.sessions.concurrent); a new sign-in ends the oldest beyond the limit.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Set the limit the organization requires.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/portal-sessions.ts (open() ends sessions beyond the concurrent limit)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-portal-sessions.test.ts (Oldest session ended at the limit)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AC-11</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Device Lock</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Access Control</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">implemented</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">After 15 minutes without activity (security.sessions.idleMinutes) the portal signs the person out and returns to the sign-in screen, and the server ends the session independently, so an unattended browser requires re-authentication through the identity provider.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Apply operating-system screen locks on endpoints.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/web/src/App.tsx (Idle timer signs out at the configured limit)
+apps/server/src/agent/portal-sessions.ts (Server-side idle limit)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-portal-sessions.test.ts (Idle session ends and cannot be reopened)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AC-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Session Termination</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Access Control</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">implemented</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Portal sessions are recorded on the server. Each sign-in opens a session that ends after 15 minutes without activity, after 12 hours however active it is, or on sign-out, which ends it on the server so a copied cookie stops working (security.sessions in papyrus.yaml sets the limits). The signed cookie carries only the session identifier and identity; each request is checked against the session record, and ending a session is audited.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Set identity-provider token lifetimes and sign-in frequency; choose session limits in papyrus.yaml that meet the organization's policy.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/portal-sessions.ts (Server-side sessions: idle limit, maximum lifetime, concurrent cap, end on sign-out)
+apps/server/src/agent/auth.ts (Cookie carries the session id; each request is checked; auth.session_end audited)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-portal-sessions.test.ts (Idle, maximum lifetime, sign-out replay and concurrent cap)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AC-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Security and Privacy Attributes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Access Control</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">partial</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">With security.classification set in papyrus.yaml, every screen, including sign-in and the Terms page, carries the system-high classification banner at the top in the standard colours (UNCLASSIFIED through TOP SECRET//SCI).</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Set the system-high classification; apply marking to documents and media under the organization's marking policy.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/http.ts (classification published in /api/config/public)
+apps/web/src/App.tsx (ClassificationBanner on every screen)
+packages/contracts/src/index.ts (CLASSIFICATION_BANNERS colours and labels)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Files Papyrus generates (PDF, DOCX, XLSX, exports) are not marked, and records carry no per-item classification.
+Remediation: Stamp the system-high marking on generated files and exports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">AU-2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="2">
+      <c r="B13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Event Logging</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="2">
+      <c r="C13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit and Accountability</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr" s="2">
+      <c r="D13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Papyrus records integration lifecycle events and action-ledger decisions (proposed, approved, denied, executed) in a hash-chained event table; role grants and revocations; every MCP tool call and MCP administrative change; API key creation, rotation and revocation; policy versions and policy denials; governed change requests and approvals; and agent traces and logs in a separate observability store.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr" s="2">
+      <c r="F13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus writes one append-only audit trail of security events: successful and failed sign-ins, sign-outs, sessions ended for inactivity or age, acknowledgement of the system use notice, every refused request (401 and 403) with its route, acceptance of the Terms, and audit export tests. Separate append-only records cover role grants and revocations, every MCP tool call and MCP administrative change, API key lifecycle, policy decisions, configuration at each start, integration and action-ledger events, and agent signatures and evidence.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Decide which additional events the organization requires and collect Entra sign-in logs from Microsoft.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/database.ts (appendEvent and recordActionEvent write the SHA-256 chained agent_integration_events table)
-apps/server/src/agent/role-assignments.ts (papyrus_role_assignment_events)
-apps/server/src/agent/mcp/calls.ts (papyrus_mcp_calls records every MCP call)
-apps/server/src/agent/mcp/tools.ts (papyrus_mcp_admin_events records classification changes)
-apps/server/src/agent/policies/store.ts (policy_history, governed_changes and policy_decisions)
-apps/server/src/agent/api-keys.ts (API key events)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr" s="2">
+      <c r="H13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/audit/log.ts (papyrus_audit_events: one schema, append-only)
+apps/server/src/agent/http.ts (Sign-in, sign-out, notice, terms and access.denied records)
+apps/server/src/agent/auth.ts (Session end records)
+apps/server/src/agent/mcp/calls.ts (MCP call records)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-integrations.test.ts (Lifecycle events are appended and the chain verifies)
 apps/server/tests/agent-mcp-stores.test.ts (Records who classified an MCP tool)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Successful and failed sign-ins and authorization denials (401/403) are not written to a local audit record. A successful sign-in is only sent as an analytics event to Beag Labs on registered deployments.
-Remediation: Write sign-in success, sign-in failure and authorization-denied events to an append-only local audit table with actor, time, route and outcome.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr" s="2">
+      <c r="J13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Document downloads, session and workflow deletions, and agent tool calls are recorded in their own stores or not at all, rather than in the unified audit trail.
+Remediation: Write these events to the unified audit trail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">AU-3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="2">
+      <c r="B14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Content of Audit Records</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="2">
+      <c r="C14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit and Accountability</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr" s="2">
+      <c r="D14" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">provider</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr" s="2">
+      <c r="E14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">implemented</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Unified audit records carry a sequence number, an ISO 8601 UTC time, the action, the outcome (success, failure or denied), the actor and the person an agent acted for, the target, the client network address, user agent, request ID and session ID, and event detail without secrets or document content. MCP call records add session, workflow, tool classification, approval ID, duration and a SHA-256 of the arguments.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/audit/log.ts (AuditEvent fields; auditRequest takes the socket address, never a forwarded header)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-local-secrets.test.ts (Key create/replace/delete does not leak secret values into audit events)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AU-4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Audit Log Storage Capacity</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Audit and Accountability</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Audit rows carry an ISO 8601 UTC timestamp, the actor's Entra object ID, the action, the affected integration, tool or resource, and the outcome. MCP call records add session, workflow, tool classification, approval ID, duration and a SHA-256 of the arguments; write calls keep the approved arguments, while tokens and results are never stored. Configuration events exclude secret values.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/database.ts (Event payload: sequence, integration, actor, action, time, data, previous hash)
-apps/server/src/agent/mcp/calls.ts (McpCallAudit columns and the rule that tokens and results are not stored)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-local-secrets.test.ts (Key create/replace/delete does not leak secret values into audit events)</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Audit records do not capture the client network address, and each log uses its own schema, so records cannot be correlated or exported in one format.
-Remediation: Add source address and request ID to audit writes and define a common audit event schema used by all append-only logs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr" s="2">
+      <c r="F15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Audit records are kept in the Papyrus data directory and, when audit.otlp is configured, delivered to the organization's collector; records written while the collector is unreachable are sent when it returns, and the backlog is shown on the Audit page.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Size the data volume and the collector's storage for the retention period the organization requires.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/audit/otlp.ts (Durable export cursor and backlog)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus does not watch free space on the data volume or alert when it runs low.
+Remediation: Add capacity monitoring and an alert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">AU-6</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr" s="2">
+      <c r="B16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="2">
+      <c r="C16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit and Accountability</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">partial</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Holders of Papyrus.Audit.View can read integration and action-ledger event history, and System Owners, Audit Viewers and Security Managers can read agent traces and logs through the observability API.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr" s="2">
+      <c r="D16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">implemented</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">System Owners and Audit Viewers review the trail on the Audit page: search by person or action, filter by outcome and time range, read each record in full, and export the filtered list as CSV or JSONL. The same records are sent to the organization's OpenTelemetry collector (OTLP/HTTP, with optional CA and mutual TLS) for review in its SIEM, at least once, resuming after an outage; the page shows the export's health and can send a test record.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Set review cadence, alerting and escalation, and correlate Papyrus records with Entra and host logs in the organization's monitoring system.</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/service.ts (Integration events require Papyrus.Audit.View)
-apps/server/src/agent/http.ts (/api/observability/traces and /logs gated by OBSERVABILITY_APP_ROLES)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-observability.test.ts (Allows each observability role to read traces and logs and rejects others)</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">There is no consolidated audit view and no export or forwarding of audit records to an external log store or SIEM; records stay in local SQLite databases.
-Remediation: Provide an audit export API and a streaming forwarder (syslog or OTLP) covering all append-only logs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr" s="2">
+      <c r="H16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/audit/otlp.ts (OTLP exporter: durable cursor, retry with backoff, TLS and mTLS)
+apps/web/src/Audit.tsx (Audit page: filters, detail, CSV/JSONL export, export status)
+apps/server/src/agent/http.ts (/api/audit/* require System Owner or Audit View; API keys refused)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-audit-otlp.test.ts (Records exported once, with headers, resuming after a collector failure)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">AU-8</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr" s="2">
+      <c r="B17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Time Stamps</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr" s="2">
+      <c r="C17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit and Accountability</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr" s="2">
+      <c r="D17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr" s="2">
+      <c r="F17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Papyrus writes audit timestamps as ISO 8601 UTC strings taken from the host clock.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr" s="2">
+      <c r="G17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Synchronize the host clock to an authoritative time source.</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr" s="2">
+      <c r="H17" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/role-assignments.ts (new Date().toISOString() on each event)
 apps/server/src/agent/mcp/calls.ts (Call timestamps in ISO 8601 UTC)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr" s="2">
+      <c r="I17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">AU-9</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="2">
+      <c r="B18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Protection of Audit Information</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="2">
+      <c r="C18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit and Accountability</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr" s="2">
+      <c r="D18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Audit tables are append-only at the database layer: SQLite triggers abort UPDATE and DELETE on integration events, model events, role assignment events, MCP admin events and settled MCP call records. Integration and action-ledger events are additionally SHA-256 hash-chained, and the chain can be recomputed to detect modification.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr" s="2">
+      <c r="F18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Audit tables are append-only at the database layer: triggers abort UPDATE and DELETE on the unified audit trail and on role, configuration, MCP, integration and model event tables; integration and action-ledger events are additionally SHA-256 hash-chained. With OTLP export configured, every record is also held by a collector outside the Papyrus host.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Restrict host and database-file access, protect backups, and copy audit records to independently controlled immutable storage.</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr" s="2">
+      <c r="H18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/database.ts (No-update/no-delete triggers and verifyEventChain)
 apps/server/src/agent/mcp/calls.ts (Append-only triggers on papyrus_mcp_calls)
 docs/security.md (States that a host or database administrator can replace local state)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr" s="2">
+      <c r="I18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-integrations.test.ts (verifyEventChain reports a valid chain after lifecycle changes)
 apps/server/tests/agent-smoke.test.ts (Event chain verifies after an end-to-end run)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Triggers and the hash chain detect changes made through the application only; anyone with write access to the database file can rewrite them. Chain verification is not exposed through any API or run on a schedule, and logs other than integration and action events are not hash-chained.
-Remediation: Expose chain verification to Audit Viewers, run it periodically, extend chaining to all audit tables, and anchor chain heads in external storage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr" s="2">
+      <c r="J18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Triggers detect changes made through the application only; anyone with write access to the database file can rewrite local records, and the unified trail is not hash-chained or signed. Off-host export mitigates this only when configured.
+Remediation: Chain and sign the unified trail with a key held outside the data directory and verify it on a schedule; require OTLP export on classified deployments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">AU-12</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="2">
+      <c r="B19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit Record Generation</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="2">
+      <c r="C19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit and Accountability</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr" s="2">
+      <c r="D19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">provider</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr" s="2">
+      <c r="E19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr" s="2">
+      <c r="F19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Audit records are generated server-side at the enforcement points themselves: the proposal approval and denial paths, the single MCP call path, role assignment changes, API key management and policy enforcement. They are therefore produced the same way regardless of which client made the request.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr" s="2">
+      <c r="G19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/service.ts (approveProposal and denyProposal call recordActionEvent)
 apps/server/src/agent/mcp/calls.ts (executeMcpTool writes start and finish records around every call)
 apps/server/src/agent/policies/store.ts (assert records each denial in policy_decisions)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr" s="2">
+      <c r="I19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-integrations.test.ts (Event count and chain after integration operations)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr" s="2">
+      <c r="J19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CM-2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr" s="2">
+      <c r="B20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Baseline Configuration</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr" s="2">
+      <c r="C20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Management</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr" s="2">
+      <c r="D20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Papyrus ships one Dockerfile that builds a Wolfi-based runtime image running as a non-root user with no browser engine, plus a DoD variant that defaults to the DoD Microsoft cloud and embeds the offline license authority key. The Azure Marketplace appliance is provisioned by script: the container listens only on 127.0.0.1 behind an nginx TLS edge. Three deployment profiles (commercial, government, disconnected) set runtime posture.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr" s="2">
+      <c r="F20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus ships one container image: Amazon Linux 2023 minimal with OpenSSL's certified FIPS provider forced on, running as a non-root user with no browser engine, scanned in CI against the DISA STIG profile for Amazon Linux 2023. Runtime configuration comes from papyrus.yaml, a reviewable file in which secrets appear only as file or environment references, and its digest and effective settings are recorded at every start. Three deployment profiles (commercial, government, disconnected) set network posture.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Document the approved deployment configuration: host OS, network, Entra registration, model endpoint, storage and the Papyrus image digest.</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr" s="2">
+      <c r="H20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Dockerfile (Build and runtime stages, nonroot user, dod target)
 deploy/marketplace/vm/provision.sh (Appliance provisioning, loopback port binding, nginx TLS edge)
 docs/deployment.md (Deployment profiles and required settings)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-app-connectors.test.ts (Keeps Chromium and agent-browser out of the hardened core image)</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr" s="2">
+      <c r="I20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-image-and-catalog.test.ts (Keeps Chromium and agent-browser out of the hardened core image)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">The baseline is not fully reproducible: base images are referenced by tag rather than digest, apk packages are not version-pinned, and several Python packages in the runtime image (pypdf, pypdfium2, reportlab, pillow) are unpinned.
 Remediation: Pin base images by digest and pin apk and pip package versions, with an automated update process that opens reviewed changes.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr" s="2">
+    <row r="21">
+      <c r="A21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CM-3</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr" s="2">
+      <c r="B21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Change Control</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr" s="2">
+      <c r="C21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Management</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr" s="2">
+      <c r="D21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">In-application changes that weaken policy, alter Classes non-additively, or publish Apps become digest-checked governed changes that apply only after a Governance principal approves them, and an approval is refused if the change's digest or expected version no longer matches. Papyrus software updates are announced by exact image digest from an allowed repository and installed only when a System Owner applies them or within an owner-configured maintenance window.</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr" s="2">
+      <c r="F21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">In-application changes that weaken policy become digest-checked governed changes that apply only after a Governance principal approves them, and an approval is refused if the change's digest or expected version no longer matches. Papyrus software updates are announced by exact image digest from an allowed repository and installed only when a System Owner applies them or within an owner-configured maintenance window.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Operate organizational change control for deployment configuration, infrastructure and when updates are applied.</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr" s="2">
+      <c r="H21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/policies/store.ts (propose/approve with digest and expected-version checks)
 apps/server/src/agent/updates/service.ts (Digest-only releases from allowed repositories; apply only the announced release)
-apps/server/src/agent/apps/http.ts (/api/governed-changes approval route)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr" s="2">
+apps/server/src/agent/policies/http.ts (/api/governed-changes approval route)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-policies.test.ts (Approved change commits atomically; a stale approval is rolled back without relaxing rules)
-apps/server/tests/agent-updates.test.ts (Accepts only exact digests from allowed repositories and applies only when asked or in the window)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr" s="2">
+apps/server/tests/agent-updates.test.ts (Accepts only exact digests from allowed repositories and applies only when asked or in the window)
+apps/server/tests/agent-policies-http.test.ts (A relaxation waits as a governed change and applies only on approval)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CM-5</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr" s="2">
+      <c r="B22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Access Restrictions for Change</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr" s="2">
+      <c r="C22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Management</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr" s="2">
+      <c r="D22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr" s="2">
+      <c r="F22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration endpoints require specific roles on the server: Integration.Manage for model gateways, MCP servers, imported APIs, package mirrors, browser and mainframe settings and branding; System Owner for role assignments, updates, license activation and skill approval; Governance for governed changes. Model API keys are accepted only over HTTPS from the portal origin.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr" s="2">
+      <c r="G22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Control access to the host, container runtime, data directory, secret stores and deployment pipeline.</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr" s="2">
+      <c r="H22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/http.ts (requireRole checks on configuration routes; requireSecretTransport)
 apps/server/src/agent/policies/store.ts (requireGovernance)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-local-secrets-http.test.ts (Requires identity and management permission; rejects cross-origin and non-HTTPS remote writes)
-apps/server/tests/agent-updates.test.ts (Only admins see and configure updates)</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr" s="2">
+      <c r="I22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-updates.test.ts (Only admins see and configure updates)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CM-6</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr" s="2">
+      <c r="B23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Settings</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr" s="2">
+      <c r="C23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Management</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr" s="2">
+      <c r="D23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Configuration is validated at startup and fails closed: persistent mode requires an HTTPS public origin and an Entra tenant and client ID; the development identity is accepted only in local mode; unknown profiles, national clouds and sandbox backends are rejected; TLS certificate and key must be set together; and the former license-bypass setting is refused. Once an HTTPS origin is configured, Host and X-Forwarded-Host headers cannot change OAuth redirect URIs or cookies.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr" s="2">
+      <c r="F23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Configuration is validated at startup and fails closed: papyrus.yaml is checked against its schema (unknown keys and bad values stop startup), an identity provider is required, persistent mode requires an HTTPS public origin, the license named in license.file must verify for this deployment, and the former development and license bypasses are refused. Every start records which file was used, its digest and each effective setting with where it came from, and flags a change from the previous start.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Choose values appropriate to the authorization boundary and verify them at deployment. In Azure Government or other national clouds, set PAPYRUS_AZURE_MANAGEMENT_ENDPOINT, PAPYRUS_AZURE_MANAGEMENT_RESOURCE, PAPYRUS_AZURE_KEYVAULT_DNS_SUFFIX and PAPYRUS_AZURE_KEYVAULT_RESOURCE; they default to Azure commercial endpoints and are not derived from PAPYRUS_ENTRA_CLOUD.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/config.ts (loadAgentConfig validation; deriveOrigin; rejectLicenseBypass)
-apps/server/src/agent/azure-key-vault.ts (Azure management and Key Vault endpoints default to commercial cloud unless overridden)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr" s="2">
+      <c r="H23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/config-file.ts (papyrus.yaml schema and loader)
+apps/server/src/agent/config-audit.ts (Configuration recorded at each start)
+apps/server/src/index.ts (license.file activated at startup or startup stops)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-config-origin.test.ts (HTTPS configured origin is authoritative over Host headers)
 apps/server/tests/security-invariants.test.ts (Government cloud selection explicit; unknown sandbox backends rejected)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr" s="2">
+      <c r="J23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CM-7</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr" s="2">
+      <c r="B24" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Least Functionality</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr" s="2">
+      <c r="C24" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Management</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr" s="2">
+      <c r="D24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">The runtime image contains no browser engine. The Papyrus agent has no general shell: native programs run only through structured executors (Python, Pandoc, LibreOffice) with fixed executables. MCP has no stdio transport. The public scheduler CRUD surface is not exposed, and removed legacy connectors read back as retired and cannot be activated or executed. The Factory sidecar that builds Apps is a separate process with its own command sandbox (see sc-39).</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr" s="2">
+      <c r="F24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The runtime image contains no browser engine. The Papyrus agent has no general shell: native programs run only through structured executors (Python, Pandoc, LibreOffice) with fixed executables. MCP has no stdio transport. The public scheduler CRUD surface is not exposed, and removed legacy connectors read back as retired and cannot be activated or executed.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Expose only ports 80/443 (and SSH if needed), and disable integrations and model endpoints the organization does not use.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr" s="2">
+      <c r="H24" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Dockerfile (Runtime stage installs no Chromium or agent-browser)
 apps/server/src/agent/mastra/workspace-executors.ts (Structured executors with fixed executables)
@@ -1113,112 +1370,112 @@
 apps/server/src/agent/database.ts (Rows for removed connectors read as retired)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-app-connectors.test.ts (No Chromium or agent-browser in the core image; removed connectors are retired)
+      <c r="I24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-image-and-catalog.test.ts (No Chromium or agent-browser in the core image; removed connectors are retired)
 apps/server/tests/agent-workspace.test.ts (Process execution kept behind structured executors)
 apps/server/tests/agent-mcp-stores.test.ts (Refuses stdio and private addresses)
 apps/server/tests/agent-http.test.ts (Scheduler portal APIs are not exposed)</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr" s="2">
+      <c r="J24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CM-8</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr" s="2">
+      <c r="B25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System Component Inventory</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr" s="2">
+      <c r="C25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Management</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr" s="2">
+      <c r="D25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr" s="2">
+      <c r="F25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">A generator produces an SPDX 2.3 SBOM of every package in the pnpm lockfile, checked for drift by the pre-commit hook, and the container workflow generates a CycloneDX SBOM of the built image.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr" s="2">
+      <c r="G25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Inventory the host OS, container runtime, reverse proxy, model endpoints and other infrastructure in the boundary.</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr" s="2">
+      <c r="H25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">scripts/compliance/generate.mjs (SPDX SBOM generation from pnpm-lock.yaml)
 compliance/sbom.spdx.json (Generated source SBOM)
 .github/workflows/container.yml (anchore/sbom-action CycloneDX image SBOM)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr" s="2">
+      <c r="I25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">The SPDX SBOM records name and version only (licenses and download locations are NOASSERTION) and omits OS and Python packages; the image SBOM is not attached to the published image as a signed attestation.
 Remediation: Publish the image SBOM as a signed attestation alongside the provenance attestation and include license data.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr" s="2">
+    <row r="26">
+      <c r="A26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CM-14</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr" s="2">
+      <c r="B26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Signed Components</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr" s="2">
+      <c r="C26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configuration Management</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr" s="2">
+      <c r="D26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr" s="2">
+      <c r="F26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Release images are signed with Cosign keyless signing in GitHub Actions. On the Azure Marketplace appliance the updater runs cosign verify against a pinned signer identity and issuer before pulling an update and installs nothing if verification fails; the Marketplace image pipeline verifies the signature and build provenance of the container digest before baking it.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr" s="2">
+      <c r="G26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">On self-hosted deployments, verify the image signature and digest before deployment.</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr" s="2">
+      <c r="H26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">deploy/marketplace/vm/papyrus-update.sh (cosign verify with PAPYRUS_UPDATE_SIGNER_IDENTITY before install)
 deploy/marketplace/vm/provision.sh (Pinned cosign binary checksum and signer identity)
@@ -1227,215 +1484,214 @@
 deploy/azure/main.bicep (Azure template references ghcr.io/beaglabs/papyrus:0.1.1 by tag)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr" s="2">
+      <c r="I26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-updates.test.ts (Update service accepts only exact digests from allowed repositories)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr" s="2">
+      <c r="J26" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Signature verification exists only on the Marketplace VM update and image-build paths; the shell updater has no automated test, and other deployment paths do not verify signatures in this repository. The Azure template (deploy/azure/main.bicep) references ghcr.io/beaglabs/papyrus:0.1.1 by tag, a different repository from the one CI publishes (ghcr.io/beaglabs/papyrus/papyrus). Two workflows (container.yml and container-multiarch.yml) sign images for the same repository while the updater trusts only the container.yml identity.
 Remediation: Settle on one signing workflow and identity, reference images by digest from the published repository in every deployment template, add an automated test for the updater verification step, and document signature verification for every supported deployment path.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr" s="2">
+    <row r="27">
+      <c r="A27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">CP-9</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr" s="2">
+      <c r="B27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System Backup</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr" s="2">
+      <c r="C27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Contingency Planning</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr" s="2">
+      <c r="D27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">customer</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr" s="2">
+      <c r="E27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">customer</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr" s="2">
+      <c r="F27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Papyrus keeps its state in the data directory (agent.db, mastra.db, jobs.db, observability.db, secrets.db and AgentFS) and documents which files must be backed up together and that the local master key must be backed up separately. It provides no backup tooling.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr" s="2">
+      <c r="G27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Back up the data directory consistently, store the master key and Key Vault recovery separately, and test restoration.</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr" s="2">
+      <c r="H27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">docs/deployment.md (Lists the databases to back up and master key handling)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr" s="2">
+      <c r="I27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">IA-2</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr" s="2">
+      <c r="B28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr" s="2">
+      <c r="C28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Identification and Authentication</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr" s="2">
+      <c r="D28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">People authenticate only through Microsoft Entra ID. Direct sign-in uses the authorization code flow with PKCE (S256), single-use state and a nonce; ID tokens are verified against the tenant's published keys for issuer, audience (client ID or api:// form), expiry, nonce and tenant ID, and discovery metadata with an unexpected issuer is rejected. Brokered sign-in redeems a one-time handle server-to-server and accepts only an assertion signed by a configured license authority key, addressed to this deployment, matching the pending login nonce and bound tenant, and unexpired. Multi-factor and PIV/CAC requirements are enforced by Entra, not by Papyrus.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Require MFA or phishing-resistant authentication through Entra Conditional Access. Brokered deployments trust Beag Labs' control plane to run the Microsoft sign-in; organizations that cannot accept that should use their own app registration.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/entra-auth.ts (startLogin, completeLogin, verifyEntraToken, completeBrokeredLogin)
-apps/server/src/agent/microsoft-broker.ts (MicrosoftBroker.verify checks signature, aud, nonce, tenant and expiry)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-microsoft-broker.test.ts (Accepts only a fresh assertion signed for this deployment, tenant and login)
-apps/server/tests/agent-auth-profile.test.ts (Interactive login requests the expected scopes per national cloud)
+      <c r="F28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">People authenticate only through the organization's OpenID Connect provider or Microsoft Entra ID. Before sign-in starts, a configured system use notice must be acknowledged. Sign-in uses the authorization code flow with PKCE (S256), single-use state and a nonce; ID tokens are verified against the provider's published keys for issuer, audience, expiry and nonce. Multi-factor and PIV/CAC requirements are enforced by the identity provider, not by Papyrus.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Require MFA or phishing-resistant authentication through Entra Conditional Access.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/auth.ts (startLogin, completeLogin, verifyEntraToken, completeBrokeredLogin)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-auth-profile.test.ts (Interactive login requests the expected scopes per national cloud)
 apps/server/tests/agent-api-keys-http.test.ts (An API key is not accepted as an Entra sign-in)</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr" s="2">
+      <c r="J28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus does not itself require multi-factor or certificate-based authentication (it trusts the identity provider's policy) and cannot accept client certificates (CAC/PIV or SIPR tokens) directly.
+Remediation: Optionally require MFA or smart-card authentication methods in the token (amr/acr), and support mutual TLS with NSS PKI where the enclave requires it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">IA-4</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr" s="2">
+      <c r="B29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Identifier Management</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr" s="2">
+      <c r="C29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Identification and Authentication</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr" s="2">
+      <c r="D29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr" s="2">
+      <c r="F29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Papyrus identifies people by Entra object ID and tenant ID and creates no identifiers of its own for people. API keys receive a random 12-hex-character identifier, and each deployment has its own deployment ID.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr" s="2">
+      <c r="G29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Manage identifier issuance and reuse policy in Entra ID.</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/entra-auth.ts (principalFromClaims requires oid and tid)
+      <c r="H29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/auth.ts (principalFromClaims requires oid and tid)
 apps/server/src/agent/api-keys.ts (Random key identifiers)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr" s="2">
+      <c r="I29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-auth.test.ts (Identity derived from Entra claims only)</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr" s="2">
+      <c r="J29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">IA-5</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="2">
+      <c r="B30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Authenticator Management</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr" s="2">
+      <c r="C30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Identification and Authentication</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr" s="2">
+      <c r="D30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr" s="2">
+      <c r="F30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">API key secrets are 32 random bytes, shown once with cache-control no-store, and stored only as an HMAC-SHA-256 keyed with the deployment secret, so a copied database cannot be used to call the API. Keys expire, can be rotated (the old secret stops immediately) and revoked. Integration settings reject inline passwords, tokens and keys and store only credential references, and model API keys are accepted only over HTTPS from the portal origin. The pre-commit hook scans staged changes for private keys and common token formats.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr" s="2">
+      <c r="G30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Manage Entra authenticators (MFA methods, certificates, client secrets) and rotate API keys on the organization's schedule.</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr" s="2">
+      <c r="H30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/api-keys.ts (Secret generation, HMAC storage, expiry, rotation and revocation)
 apps/server/src/agent/service.ts (rejectInlineSecrets on integration settings)
@@ -1443,388 +1699,430 @@
 scripts/hooks/secret-scan.mjs (Pre-commit secret pattern scan)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr" s="2">
+      <c r="I30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/api-keys.test.ts (Secret shown once and not stored; useless under another deployment secret; expiry, rotation, revocation)
 apps/server/tests/agent-integrations.test.ts (Rejects inline connector secrets and stores only references)</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr" s="2">
+      <c r="J30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">IA-8</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="2">
+      <c r="B31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Identification and Authentication (Non-Organizational Users)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr" s="2">
+      <c r="C31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Identification and Authentication</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr" s="2">
+      <c r="D31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Only tokens issued for the bound Entra tenant are accepted, so any external person must exist in that tenant (for example as a guest). The only unauthenticated routes for the public are Resource Class public forms, single-use request links and signed webhooks; each answers only for an active endpoint, accepts only that endpoint's configured fields, and cannot write person, group or reference fields.</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Decide whether guests may be assigned Papyrus roles, and approve which Class endpoints are public.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/entra-auth.ts (WRONG_ENTRA_TENANT check)
-apps/server/src/agent/classes/http.ts (handlePublicIntake, handlePublicRequest, handleWebhook)
-apps/server/src/agent/classes/webhooks.ts (Constant-time signature check with 300-second tolerance)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-class-endpoints-http.test.ts (Public form takes only its fields; submitter sees only their own record)
-apps/server/tests/agent-class-requests-webhooks.test.ts (Request links single-use and lockable; webhooks signature-checked and deduplicated)</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr" s="2">
+      <c r="F31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Only tokens issued for the bound Entra tenant are accepted, so any external person must exist in that tenant (for example as a guest). The only unauthenticated route for other systems is a workflow webhook (/hooks/&lt;id&gt;): it answers only for a published workflow with a webhook trigger, requires a signature made with the server-generated secret, and only starts that workflow with the event as its input.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Decide whether guests may be assigned Papyrus roles, and which workflows other systems may start by webhook.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/auth.ts (WRONG_ENTRA_TENANT check)
+apps/server/src/agent/workflow-webhooks.ts (Constant-time signature check with 300-second tolerance; one run per event id)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-workflow-webhook-http.test.ts (Signed event starts exactly one run; bad signature 401; unpublished workflow 404)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">IR-4</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr" s="2">
+      <c r="B32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Incident Handling</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr" s="2">
+      <c r="C32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Incident Response</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr" s="2">
+      <c r="D32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">customer</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr" s="2">
+      <c r="E32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">customer</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr" s="2">
+      <c r="F32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Papyrus provides no incident handling capability or plan. Its audit and observability records are inputs to the deploying organization's process.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr" s="2">
+      <c r="G32" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Maintain and exercise an incident response plan covering the Papyrus deployment, including revoking roles, API keys and connector credentials and preserving audit databases.</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr" s="2">
+      <c r="H32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">RA-5</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr" s="2">
+      <c r="B33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr" s="2">
+      <c r="C33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Risk Assessment</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">planned</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Beag Labs does not currently run automated vulnerability scanning of dependencies, source code or container images in CI. The SBOMs described under cm-8 are available as scanning inputs.</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr" s="2">
+      <c r="D33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">partial</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CI scans each built image against the DISA STIG SCAP profile for Amazon Linux 2023, and the published evidence pack includes Trivy vulnerability scans of every platform of the released image. Dependency and static-analysis scanning do not run in CI.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Scan hosts, the deployed image and surrounding infrastructure with the organization's tools.</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr" s="2">
+      <c r="H33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">.github/workflows/container.yml (Generates an image SBOM; contains no scanning step)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">No dependency, static-analysis or image vulnerability scanning runs in CI, and there is no Dependabot or equivalent configuration.
-Remediation: Add image and dependency scanning (for example Grype or Trivy against the CycloneDX SBOM) and static analysis to CI, failing builds on critical findings, and enable automated dependency update pull requests.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr" s="2">
+      <c r="I33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">No dependency or static-analysis scanning runs in CI, and there are no severity-based remediation timeframes.
+Remediation: Add dependency and code scanning to CI and publish remediation timeframes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SA-9</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr" s="2">
+      <c r="B34" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">External System Services</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr" s="2">
+      <c r="C34" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Services Acquisition</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr" s="2">
+      <c r="D34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">implemented</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus calls no Beag Labs service: licenses are verified locally against keys built into Papyrus, sign-in uses the organization's own identity provider, and the Terms and Privacy Policy ship inside the app. Sentry error reporting is off unless a DSN is set and runs with sendDefaultPii disabled.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Assess the configured model gateway, MCP servers and any Sentry DSN as external services.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/license.ts (Local signature verification against the built-in license authorities)
+apps/server/src/agent/sentry.ts (Sentry initialized only with a DSN, sendDefaultPii false)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-license-authorities.test.ts (Only the built-in authorities verify licenses)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SA-11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Developer Testing and Evaluation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">System and Services Acquisition</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">provider</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Connected deployments call Beag Labs services outbound only: registration, signed deployment status, brokered sign-in, staff-directory Graph tokens, analytics, and on control-plane deployments hourly agent-execution usage reports to papyrus.beaglabs.com/api/deployments/usage. Status and identity responses are accepted only when signed by a configured license authority key and addressed to this deployment, and the control plane URL must be HTTPS. Registration is skipped for the disconnected profile or when PAPYRUS_BEAGLABS_REGISTRATION=0. Other outbound services the code can call are huggingface.co (embedding model download on first use unless PAPYRUS_EMBEDDING_DOWNLOAD=0), GitHub or GitLab from the Factory when configured, public package registries for skill and session installs unless PAPYRUS_PACKAGE_PUBLIC_REGISTRIES=false or the profile is disconnected, and Sentry only when a DSN is set (with sendDefaultPii disabled).</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Assess Beag Labs as an external service provider, or use the disconnected profile or set PAPYRUS_BEAGLABS_REGISTRATION=0 to avoid it.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/control-plane.ts (verifySignedStatus; HTTPS required for PAPYRUS_CONTROL_PLANE_URL)
-apps/server/src/agent/microsoft-broker.ts (All broker calls are outbound with the deployment key)
-apps/server/src/agent/provisioning-control-plane.ts (Registration disabled for disconnected profile or PAPYRUS_BEAGLABS_REGISTRATION=0)
-apps/server/src/agent/beaglabs-analytics.ts (Analytics batches sent to Beag Labs after registration)
-apps/server/src/agent/sentry.ts (Sentry initialized only with a DSN, sendDefaultPii false)
-apps/server/src/agent/execution-usage.ts (postUsage sends execution usage to /api/deployments/usage)
-scripts/embedding-model.mjs (Downloads the embedding model from huggingface.co unless PAPYRUS_EMBEDDING_DOWNLOAD=0)
-apps/server/src/agent/mastra-factory/app-source.ts (GitHub API default for Factory source)
-apps/server/src/agent/http.ts (analytics.identify on sign-in with display name and tenant ID)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-control-plane.test.ts (Rejects bad signatures, expired status and other deployments' status)
-apps/server/tests/agent-beaglabs-analytics.test.ts (Queues until registered, then batches with deployment authentication)</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">On registered deployments the server sends each person's Entra object ID, display name and tenant ID to Beag Labs as analytics on sign-in, and there is no setting to turn analytics off separately from registration. Deployments on the government profile register with Beag Labs unless PAPYRUS_BEAGLABS_REGISTRATION=0 is set. Several outbound destinations (embedding download, package registries) are not listed in docs/deployment.md. The control plane and license authority are not in this repository and are not covered by this assessment.
-Remediation: Add a separate analytics opt-out and stop sending display names, default registration off for the government profile, document every outbound destination with its switch, and publish a security description of the control plane and license authority.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">SA-11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Developer Testing and Evaluation</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">System and Services Acquisition</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">provider</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">partial</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">The repository has workspace-wide TypeScript type checking and a Vitest suite for the server covering identity, authorization, MCP, Resource Classes, secrets, sandboxing and approvals. CI runs type checking and a fixed subset of tests (Factory, scoped workflows, mainframe guardrails and offline evaluations), and a local pre-commit hook runs secret, contract and compliance-drift checks plus security-invariant tests when related files change.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">.github/workflows/factory-write-qualification.yml (CI typecheck and the tests it runs)
+      <c r="F35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The repository has workspace-wide TypeScript type checking and a Vitest suite for the server covering identity, authorization, MCP, secrets, sandboxing and approvals. CI runs type checking and a fixed subset of tests (scoped workflows, mainframe guardrails, policies, execution records, channel linking and offline evaluations), and a local pre-commit hook runs secret, contract and compliance-drift checks plus security-invariant tests when related files change.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">.github/workflows/ci.yml (CI typecheck and the tests it runs)
 scripts/hooks/precommit.mjs (Pre-commit checks and conditional test runs)
 apps/server/tests/security-invariants.test.ts (Security invariant tests)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Most security tests, including identity, MCP, Resource Class intake, Key Vault, broker and control-plane tests, do not run in CI, and the compliance drift check runs only in the local pre-commit hook, which can be skipped. compliance/ssp.md states that these checks run in CI.
+      <c r="I35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Most security tests, including identity, MCP and Key Vault tests, do not run in CI, and the compliance drift check runs only in the local pre-commit hook, which can be skipped. compliance/ssp.md states that these checks run in CI.
 Remediation: Run the full server test suite and pnpm compliance:check in CI on every pull request and make them required checks.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr" s="2">
+    <row r="36">
+      <c r="A36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SC-4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Information in Shared System Resources</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">System and Communications Protection</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">provider</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">partial</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus databases are opened with SQLite secure_delete, so content removed from them is overwritten rather than left in free pages. Each agent workspace runs in its own sandboxed process with a temporary materialized workspace.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Use volume encryption and sanitize media under the organization's procedures.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/database.ts (secure_delete on agent.db)
+apps/server/src/agent/mastra/runtime.ts (secure_delete on session and trace stores)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Deleting a session does not remove every copy of its content (workspace files, traces, embeddings), and there is no administrator purge for spillage.
+Remediation: Add a cascading purge with verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-5</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr" s="2">
+      <c r="B37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Denial-of-Service Protection</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr" s="2">
+      <c r="C37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr" s="2">
+      <c r="D37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Request bodies are read under fixed byte ceilings and refused with 413 beyond them; public intake, request links and lookups are rate-limited per client and per endpoint; pending sign-ins are capped; and outbound workflow requests time out after 15 seconds with bodies limited to 256 KiB.</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr" s="2">
+      <c r="F37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Request bodies are read under fixed byte ceilings and refused with 413 beyond them; workflow webhooks are rate-limited per webhook and take bodies of at most 1 MB; pending sign-ins are capped; and outbound workflow requests time out after 15 seconds with bodies limited to 256 KiB.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Provide network-layer DoS protection and rate limiting at the reverse proxy or gateway.</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr" s="2">
+      <c r="H37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/http.ts (body() and rawBody() byte limits)
-apps/server/src/agent/classes/endpoints.ts (IntakeRateLimiter)
-apps/server/src/agent/classes/http.ts (Per-client limits for request links and lookups)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-class-endpoints-http.test.ts (Rate-limits form submissions)
-apps/server/tests/agent-http.test.ts (Refuses an oversized chat body)</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr" s="2">
+apps/server/src/agent/rate-limit.ts (MinuteRateLimiter)
+apps/server/src/agent/workflow-webhooks.ts (Per-webhook delivery limit)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-http.test.ts (Refuses an oversized chat body)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Rate limits are in memory and keyed on the socket address; behind the appliance's nginx proxy every client shares one address, and the limiter clears all windows once it tracks 10,000 keys. The cap of 256 pending sign-ins can be exhausted by unauthenticated requests, blocking sign-in for up to 10 minutes.
 Remediation: Key limits on a trusted forwarded client address, bound memory without clearing all windows, and rate-limit /api/auth/entra/login per client instead of a global cap.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr" s="2">
+    <row r="38">
+      <c r="A38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-7</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr" s="2">
+      <c r="B38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Boundary Protection</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr" s="2">
+      <c r="C38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr" s="2">
+      <c r="D38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">On the Marketplace appliance the container is published only on 127.0.0.1 and reached through nginx. Every outbound call made for MCP, OAuth discovery, workflows, imported APIs and Class endpoint sends passes one check: HTTPS, no embedded credentials, an organization denylist, and refusal of hosts that resolve to loopback, private or link-local addresses (including cloud metadata) unless listed as internal; redirects are not followed. Calls to the Beag Labs control plane are outbound only. Workspace commands have no network access.</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr" s="2">
+      <c r="F38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Workflow HTTP steps, link previews, MCP servers and repository imports pass one egress gate: HTTPS, no embedded credentials, refusal of hosts that resolve to loopback, private or link-local addresses unless listed as internal, and, when egress.allowedHosts is set (required on the disconnected profile), only listed hosts. Redirects are re-checked hop by hop. Workspace commands have no network access. On the Marketplace appliance the container is published only on 127.0.0.1 behind nginx.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Place the deployment behind the organization's firewalls and proxies, restrict inbound access to 443, and set the egress denylist and internal-host list.</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr" s="2">
+      <c r="H38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/mastra/workflow-runtime-tools.ts (assertWorkflowHttpTarget)
 apps/server/src/agent/mcp/oauth.ts (mcpFetch applies the same check and redirect: manual)
@@ -1832,112 +2130,110 @@
 apps/server/src/agent/azure-key-vault.ts (Deployment vault created with publicNetworkAccess Enabled)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr" s="2">
+      <c r="I38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/workflow-http-target.test.ts (Address classification, denylist and internal-host rules)
 apps/server/tests/agent-mcp-stores.test.ts (Refuses private addresses and plain HTTP to public hosts)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr" s="2">
+      <c r="J38" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">The address check resolves DNS separately from the connection that follows, so a host that changes its DNS answer between the two can reach an internal address. The deployment Key Vault is created with public network access enabled.
 Remediation: Connect to the address that was checked (pinned lookup) for all outbound requests, and support private endpoints or firewall rules for the deployment Key Vault.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr" s="2">
+    <row r="39">
+      <c r="A39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-8</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr" s="2">
+      <c r="B39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Transmission Confidentiality and Integrity</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr" s="2">
+      <c r="C39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr" s="2">
+      <c r="D39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Persistent mode refuses to start without an HTTPS public origin. The daemon can terminate TLS itself with a TLS 1.2 minimum, and the Marketplace appliance's nginx edge allows only TLS 1.2 and 1.3 and sends HSTS. Portal cookies are Secure under HTTPS. Outbound connections to MCP servers, workflows, imported APIs, Class endpoints and the control plane require HTTPS except for hosts the organization explicitly lists as internal.</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr" s="2">
+      <c r="F39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Persistent mode refuses to start without an HTTPS public origin. The daemon can terminate TLS itself with a TLS 1.2 minimum, and the Marketplace appliance's nginx edge allows only TLS 1.2 and 1.3 and sends HSTS. Portal cookies are Secure under HTTPS. Outbound connections to MCP servers, workflows and imported APIs require HTTPS except for hosts the organization explicitly lists as internal.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Provide certificates, TLS termination and cipher policy that meet organizational requirements.</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr" s="2">
+      <c r="H39" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/config.ts (Persistent deployments require an HTTPS PAPYRUS_PUBLIC_ORIGIN)
 apps/server/src/agent/http.ts (createHttpsServer with minVersion TLSv1.2)
-deploy/marketplace/vm/provision.sh (ssl_protocols TLSv1.2 TLSv1.3 and HSTS)
-apps/server/src/agent/control-plane.ts (PAPYRUS_CONTROL_PLANE_URL must use HTTPS)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/workflow-http-target.test.ts (Rejects plain HTTP to non-internal hosts)
-apps/server/tests/agent-local-secrets-http.test.ts (Rejects non-HTTPS remote secret entry even with spoofed forwarding headers)</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr" s="2">
+deploy/marketplace/vm/provision.sh (ssl_protocols TLSv1.2 TLSv1.3 and HSTS)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/workflow-http-target.test.ts (Rejects plain HTTP to non-internal hosts)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-12</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr" s="2">
+      <c r="B40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Cryptographic Key Establishment and Management</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr" s="2">
+      <c r="C40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr" s="2">
+      <c r="D40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr" s="2">
+      <c r="F40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">The local secrets master key must be a separately provisioned 32-byte file that is not group- or world-writable and is opened without following symlinks; the server never generates it. Where Azure Key Vault is configured, the portal secret, Entra client secret and model and provider keys are kept in a deployment Key Vault (RBAC mode, purge protection, 90-day soft delete) with only the VM's managed identity granted access, and each reader is limited to its own secret-name prefix. License authority public keys are supplied by configuration or baked into the DoD image.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr" s="2">
+      <c r="G40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Provision, back up and protect the master key and portal secret; manage Entra and TLS keys.</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr" s="2">
+      <c r="H40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/local-secrets.ts (Master key checks)
 apps/server/src/agent/deployment-vault.ts (Core vault and purpose-prefix read guard)
@@ -1945,394 +2241,385 @@
 apps/server/src/agent/openapi/credentials.ts (Connector credential key derived as SHA-256 of the portal secret)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr" s="2">
+      <c r="I40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-local-secrets.test.ts (Fails closed with missing, insecure or incorrect master keys)
 apps/server/tests/agent-deployment-vault.test.ts (Each caller reads only its own secrets; references refused without an Azure identity)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr" s="2">
+      <c r="J40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">There is no rotation or key-versioning support for the portal secret or the local master key. Encryption keys for connector credentials are derived with a single SHA-256 of the portal secret, so changing that secret makes stored values unreadable. The Key Vault uses the Standard (software-protected) tier.
 Remediation: Introduce versioned data-encryption keys with a proper KDF, a re-encryption procedure for rotation, and an option for HSM-backed keys.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr" s="2">
+    <row r="41">
+      <c r="A41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-13</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr" s="2">
+      <c r="B41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Cryptographic Protection</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr" s="2">
+      <c r="C41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">partial</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Papyrus uses the Node.js crypto module (OpenSSL) for AES-256-GCM encryption of stored credentials, HMAC-SHA-256 for cookies, API key hashes and webhook signatures, SHA-256 hash chains, SHA-256 signature verification of license, status and identity documents, and TLS; JWTs are verified with the jose library. FIPS mode is not enabled anywhere in the repository or image.</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr" s="2">
+      <c r="D41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">implemented</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The image runs OpenSSL with Amazon Linux 2023's certified FIPS 140-3 provider (CMVP #5438) forced on, and Papyrus refuses to start if FIPS mode is not active or MD5 is still allowed. Stored credentials use AES-256-GCM; cookies, API key hashes and webhook signatures use HMAC-SHA-256; hash chains use SHA-256.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Where FIPS 140 validated cryptography is required, run on a validated module and terminate TLS on validated infrastructure.</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/local-secrets.ts (AES-256-GCM)
-apps/server/src/license.ts (verifyAuthoritySignature with sha256)
-apps/server/src/agent/entra-auth.ts (HMAC-SHA-256 portal cookie; jose jwtVerify)
-Dockerfile (Runtime installs Wolfi nodejs-24; no FIPS configuration)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Papyrus does not enable OpenSSL FIPS mode or a FIPS provider, and the image is not built on a FIPS 140 validated cryptographic module. Algorithms in use are FIPS-approved, but no validated module is claimed.
-Remediation: Build a FIPS variant of the image on a FIPS 140-3 validated OpenSSL provider, enable FIPS mode at startup, fail startup if it is unavailable, and test that every code path works under it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr" s="2">
+      <c r="H41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/fips-check.ts (Startup refuses to run unless getFips() is 1 and MD5 is refused)
+Dockerfile (AL2023 with openssl-fips-provider-certified, FIPS forced)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Signatures and MACs use P-256 and SHA-256 rather than the CNSA suite (P-384, SHA-384) that national security systems may require.
+Remediation: Move Papyrus-generated signatures and MACs to CNSA algorithms while still verifying existing ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-18</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr" s="2">
+      <c r="B42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Mobile Code</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr" s="2">
+      <c r="C42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr" s="2">
+      <c r="D42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">provider</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr" s="2">
+      <c r="E42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Agent-built Hosted App and Factory preview code runs in an opaque iframe sandboxed to allow-scripts only, with a CSP of default-src 'none', connect-src 'none', form-action 'none' and base-uri 'none', loaded through a one-use frame ticket. App source that performs direct browser networking or contains credential literals or ambient secrets is rejected before release. HTML and SVG artifacts are served as attachments with a sandbox CSP.</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Optionally route a separate HTTPS App origin (PAPYRUS_APP_ORIGIN) as defense in depth.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/apps/http.ts (Sandboxed frame CSP and nonce-checked message bridge)
-apps/server/src/agent/apps/project.ts (Rejects direct browser networking in App source)
-apps/server/src/agent/factory-preview.ts (Preview sandbox CSP)
-apps/server/src/agent/http.ts (Active artifact content served as attachment with sandbox CSP)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-app-runtime-boundary.test.ts (Rejects ambient secrets, browser networking and credential literals)
-apps/server/tests/agent-app-host.test.ts (App content kept in an opaque sandbox)
-apps/server/tests/agent-factory-publication.test.ts (Public content served in a one-use opaque frame with no credentials)</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr" s="2">
+      <c r="F42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus runs no agent-built code in the browser. HTML and SVG artifacts are served as attachments with a sandbox CSP (default-src 'none'), so they cannot run in the portal's origin.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/http.ts (Active artifact content served as attachment with sandbox CSP)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-artifact-content-http.test.ts (HTML artifacts are sandboxed attachments; passive content is inline)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-23</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr" s="2">
+      <c r="B43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Session Authenticity</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr" s="2">
+      <c r="C43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="2">
+      <c r="D43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">provider</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr" s="2">
+      <c r="E43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr" s="2">
+      <c r="F43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">The portal session cookie is HMAC-SHA-256 signed with the deployment secret, compared in constant time, and set HttpOnly, SameSite=Strict, Secure and with the __Host- prefix under HTTPS. OIDC state and nonce are random 32-byte values held server-side, single-use and expiring after 10 minutes; MCP OAuth sign-ins are likewise single-use, bound to the initiating person and checked against the discovered issuer. Once an HTTPS origin is configured, request headers cannot change the origin used for redirects or cookies.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/src/agent/entra-auth.ts (portalCookie, verifyPortalCookie, pending login state)
+      <c r="G43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/src/agent/auth.ts (portalCookie, verifyPortalCookie, pending login state)
 apps/server/src/agent/mcp/oauth.ts (10-minute single-use pending sign-ins with issuer check)
 apps/server/src/agent/config.ts (deriveOrigin)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr" s="2">
+      <c r="I43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-mcp-runtime.test.ts (Refuses a callback from another person, a reused state and a different issuer)
 apps/server/tests/agent-config-origin.test.ts (HTTPS origin authoritative over Host headers)
 apps/server/tests/agent-auth-profile.test.ts (Signed cookie carries only the authority-bearing identity)</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr" s="2">
+      <c r="J43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-28</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="2">
+      <c r="B44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Protection of Information at Rest</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr" s="2">
+      <c r="C44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr" s="2">
+      <c r="D44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Papyrus encrypts secrets at the application layer with AES-256-GCM and per-record associated data: model gateway keys in a separate 0600 secrets database under a separately provisioned master key; and connector, imported-API and MCP credentials bound to their owner. Where Azure Key Vault is configured, platform secrets are stored there and configuration files hold only references.</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr" s="2">
+      <c r="F44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus encrypts secrets at the application layer with AES-256-GCM and per-record associated data: model gateway keys in a separate 0600 secrets database under a separately provisioned master key; and connector, imported-API and MCP credentials bound to their owner. Where Azure Key Vault is configured, platform secrets are stored there and configuration files hold only references. SQLite databases are opened with secure_delete, so deleted rows are overwritten rather than left in free pages.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Encrypt the volume that holds the data directory and its backups, and manage those keys.</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr" s="2">
+      <c r="H44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/local-secrets.ts (secrets.db encryption and file permissions)
 apps/server/src/agent/openapi/credentials.ts (Owner-bound AES-256-GCM connector credentials)
 apps/server/src/agent/deployment-vault.ts (Key Vault storage of platform secrets)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr" s="2">
+      <c r="I44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-local-secrets.test.ts (Encrypted persistence, tamper rejection and cross-profile binding)
 apps/server/tests/agent-mcp-stores.test.ts (Shared MCP token stored encrypted and never returned)
 apps/server/tests/agent-deployment-vault.test.ts (bootstrap.json holds only references)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Agent sessions, Library documents, Resource Class records, audit logs and traces are stored in unencrypted SQLite and AgentFS files; their protection at rest depends entirely on volume encryption that Papyrus neither provides nor checks.
-Remediation: Document volume encryption as a deployment requirement and verify it on supported deployment configurations, or add database-level encryption for the main data stores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr" s="2">
+      <c r="J44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Agent sessions, Library documents, audit records and traces are stored in unencrypted SQLite and AgentFS files; their confidentiality at rest depends on volume encryption the deploying organization provides.
+Remediation: Require and verify an encrypted volume for the data directory on classified deployments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SC-39</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr" s="2">
+      <c r="B45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Process Isolation</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr" s="2">
+      <c r="C45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Communications Protection</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr" s="2">
+      <c r="D45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">provider</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">partial</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr" s="2">
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">implemented</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Commands the Papyrus agent runs in its workspace run in a separate worker process under landstrip (Landlock and seccomp on Linux, Seatbelt on macOS) with writes limited to a temporary materialized workspace, the Papyrus data directory unreadable and network denied. The worker validates and resolves the effective policy before starting the command and refuses to run if the write root, network restriction or data-directory denial is not in effect; unsupported platforms run no workspace commands. Credential-like environment variables are removed before the command starts.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr" s="2">
+      <c r="G45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Run on a Linux host with Landlock enabled and do not run the container privileged.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr" s="2">
+      <c r="H45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/mastra/workspace-nono-worker.ts (landstrip policy, validate/resolve checks, fail-closed exits)
 apps/server/src/agent/mastra/workspace-nono.ts (Worker launch and sensitiveEnvironmentKey stripping)
-apps/server/src/agent/mastra/workspace-landstrip.ts (Read-confinement check of the resolved policy)
-apps/factory/src/mastra/index.ts (Factory sidecar constructs a Mastra LocalSandbox with only an environment allow-list, no native isolation)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr" s="2">
+apps/server/src/agent/mastra/workspace-landstrip.ts (Read-confinement check of the resolved policy)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/security-invariants.test.ts (Fails closed without OS isolation; strips credential-like environment values; rejects cwd traversal)
 apps/server/tests/agent-workspace.test.ts (Reports landstrip isolation and refuses escaping working directories)
 apps/server/tests/agent-session-workspace.test.ts (Rejects snapshots that include daemon data or parent roots)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">The Factory sidecar, enabled by default in the image (PAPYRUS_FACTORY_SIDECAR=1), runs commands for App builds in Mastra's LocalSandbox with no kernel isolation: only its environment is restricted to an allow-list. Those commands run as the same user as the daemon, can read files that user can read, including the Papyrus data directory, and have network access.
-Remediation: Run Factory sidecar commands under the same landstrip policy as agent workspace commands (data directory denied, network denied or limited to package mirrors and source control), or disable the sidecar by default until that is in place.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr" s="2">
+      <c r="J45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SI-2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr" s="2">
+      <c r="B46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Flaw Remediation</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr" s="2">
+      <c r="C46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Information Integrity</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr" s="2">
+      <c r="D46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr" s="2">
+      <c r="F46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Beag Labs publishes fixes as new signed images. A deployment learns of a release through an HMAC-signed, timestamped webhook with replay protection, and a System Owner applies it or allows it to apply within a maintenance window; the Marketplace updater verifies the image signature before installing.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr" s="2">
+      <c r="G46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Set patch windows, test updates and apply them within organizational timeframes.</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr" s="2">
+      <c r="H46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/updates/service.ts (verifyWebhook, announce, apply, maintenance window)
 deploy/marketplace/vm/papyrus-update.sh (Signature verification and install)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr" s="2">
+      <c r="I46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-updates.test.ts (Signature over timestamp and body, replay refusal, window-limited auto-apply)</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr" s="2">
+      <c r="J46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Beag Labs has no documented flaw remediation timeframes by severity, and no published security advisory or vulnerability disclosure process (no SECURITY.md).
 Remediation: Publish a vulnerability disclosure policy and severity-based remediation SLAs, and announce fixed vulnerabilities in release notes.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr" s="2">
+    <row r="47">
+      <c r="A47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SI-4</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr" s="2">
+      <c r="B47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System Monitoring</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr" s="2">
+      <c r="C47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Information Integrity</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr" s="2">
+      <c r="D47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Papyrus records agent traces and logs in a separate observability database readable by System Owners, Audit Viewers and Security Managers, writes structured JSON warnings to standard output, and can send errors to a customer-supplied Sentry DSN. The container health check verifies that the landstrip sandbox enforces its boundary; it does not check that the HTTP service is answering.</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr" s="2">
+      <c r="F47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Papyrus records agent traces and logs in a separate observability database readable by System Owners, Audit Viewers and Security Managers, writes structured JSON warnings to standard output, and can send errors to a customer-supplied Sentry DSN. Security events are written to the unified audit trail and exported to the organization's collector over OTLP when configured. The container health check verifies that the landstrip sandbox enforces its boundary; it does not check that the HTTP service is answering.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Collect container output and audit data into the organization's monitoring platform and alert on it.</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr" s="2">
+      <c r="H47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/http.ts (Observability trace and log routes)
 apps/server/src/agent/sentry.ts (Optional Sentry reporting)
@@ -2340,233 +2627,228 @@
 deploy/container/healthcheck.mjs (Health check probes landstrip write confinement only)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr" s="2">
+      <c r="I47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-observability.test.ts (Role-gated access to traces and logs)</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr" s="2">
+      <c r="J47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SI-7</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr" s="2">
+      <c r="B48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr" s="2">
+      <c r="C48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Information Integrity</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr" s="2">
+      <c r="D48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Releases are referenced by image digest and signature-verified before the Marketplace updater installs them. Hosted App publication approves an immutable, digest-checked build. Governed changes are re-hashed at approval and refused if the digest differs. The stored control-plane status is re-verified against its signature on every read, so editing the file cannot lift a suspension. Integration and action events are hash-chained.</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr" s="2">
+      <c r="F48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Releases are referenced by image digest and signature-verified before the Marketplace updater installs them. Governed changes are re-hashed at approval and refused if the digest differs. Integration and action events are hash-chained.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Verify image digests and signatures on deployment paths other than the Marketplace appliance.</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr" s="2">
+      <c r="H48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/updates/service.ts (Exact digest references only)
-apps/server/src/agent/factory-publication.ts (Digest-checked publication)
-apps/server/src/agent/policies/store.ts (CHANGE_TAMPERED digest check)
-apps/server/src/agent/control-plane.ts (readStored re-verifies the signed status)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">apps/server/tests/agent-control-plane.test.ts (An edited status file does not lift a suspension)
-apps/server/tests/agent-factory-publication.test.ts (Stale or forged publication authority is refused)
-apps/server/tests/agent-policies.test.ts (Stale approvals roll back)</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr" s="2">
+apps/server/src/agent/policies/store.ts (CHANGE_TAMPERED digest check)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">apps/server/tests/agent-policies.test.ts (Stale approvals roll back)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SI-10</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr" s="2">
+      <c r="B49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Information Input Validation</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr" s="2">
+      <c r="C49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Information Integrity</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr" s="2">
+      <c r="D49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">provider</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr" s="2">
+      <c r="E49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">implemented</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Request bodies must be JSON objects under per-route byte limits; required strings are length-bounded; policy rules are validated against a fixed schema; public forms accept only allow-listed fields and bounded uploads of permitted types and cannot reference Library paths; outbound addresses are validated before use; and webhook payloads are signature-checked over the exact raw bytes.</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr" s="2">
+      <c r="F49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Request bodies must be JSON objects under per-route byte limits; required strings are length-bounded; policy rules are validated against a fixed schema; outbound addresses are validated before use; and workflow webhook payloads are signature-checked over the exact raw bytes before they are parsed.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/http.ts (body(), rawBody(), requiredString(), boundedInteger())
 apps/server/src/agent/policies/evaluator.ts (validateRules)
-apps/server/src/agent/classes/endpoints.ts (Endpoint field validation)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr" s="2">
+apps/server/src/agent/workflow-webhooks.ts (verifyWebhook over the raw body)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-policies.test.ts (Fails closed for missing context and invalid rules)
-apps/server/tests/agent-class-endpoints-http.test.ts (Refuses other file types and Library paths)
 apps/server/tests/agent-http.test.ts (Bounds session IDs and chat bodies)</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr" s="2">
+      <c r="J49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SI-11</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr" s="2">
+      <c r="B50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Error Handling</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr" s="2">
+      <c r="C50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">System and Information Integrity</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr" s="2">
+      <c r="D50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr" s="2">
+      <c r="F50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Errors are returned as JSON with a code and a per-request ID. Known error types map to specific status codes, sign-in error pages do not echo request input, the browser connection address is masked in error text, and imported-API credentials are redacted from errors.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr" s="2">
+      <c r="G50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Configure log handling so diagnostic output is not exposed beyond administrators.</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr" s="2">
+      <c r="H50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/src/agent/http.ts (Central error mapping with requestId; INTERNAL_ERROR branch)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr" s="2">
+      <c r="I50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">apps/server/tests/agent-mcp-http.test.ts (A cancelled sign-in page does not echo anything from the address)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr" s="2">
+      <c r="J50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Unexpected exceptions are returned to the client as 500 INTERNAL_ERROR with the exception's message text, which can disclose internal details.
 Remediation: Return a generic message for unmapped errors and log the detail server-side under the request ID.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr" s="2">
+    <row r="51">
+      <c r="A51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SR-4</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr" s="2">
+      <c r="B51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Provenance</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr" s="2">
+      <c r="C51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Supply Chain Risk Management</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">shared</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr" s="2">
+      <c r="D51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">shared</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">partial</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr" s="2">
+      <c r="F51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Container images built from main are signed with Cosign and receive a GitHub build provenance attestation. Dependencies are locked in pnpm-lock.yaml and installed with --frozen-lockfile in CI, and the pnpm version is pinned with a hash in packageManager.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr" s="2">
+      <c r="G51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Retain the image digests and attestations for deployed releases and verify them at intake.</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr" s="2">
+      <c r="H51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">.github/workflows/container.yml (cosign sign and actions/attest-build-provenance)
 pnpm-lock.yaml (Locked dependency graph)
 package.json (packageManager pnpm pinned with hash)
-.github/workflows/factory-write-qualification.yml (pnpm install --frozen-lockfile)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr" s="2">
+.github/workflows/ci.yml (pnpm install --frozen-lockfile)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">GitHub Actions are referenced by mutable version tags rather than commit SHAs, and base images and OS and Python packages in the Dockerfile are not pinned, so build inputs are not fully traceable.
 Remediation: Pin all Actions to commit SHAs and pin image and package inputs (see cm-2), recording them in the provenance attestation.</t>
@@ -2574,6 +2856,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J45"/>
+  <autoFilter ref="A1:J51"/>
 </worksheet>
 </file>